--- a/Results_experiment/exp_4/preds_1111122222333222.xlsx
+++ b/Results_experiment/exp_4/preds_1111122222333222.xlsx
@@ -660,7 +660,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D2">
-        <v>1.735081315040588</v>
+        <v>1.084122896194458</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -674,7 +674,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D3">
-        <v>1.048850178718567</v>
+        <v>1.070964097976685</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -688,7 +688,7 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>2.322788000106812</v>
+        <v>1.268658876419067</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -702,7 +702,7 @@
         <v>8.5</v>
       </c>
       <c r="D5">
-        <v>7.662758827209473</v>
+        <v>7.692304611206055</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -716,7 +716,7 @@
         <v>14.80000019073486</v>
       </c>
       <c r="D6">
-        <v>6.707736968994141</v>
+        <v>9.663177490234375</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -730,7 +730,7 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>4.34116792678833</v>
+        <v>6.282390594482422</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -744,7 +744,7 @@
         <v>9.5</v>
       </c>
       <c r="D8">
-        <v>3.122756481170654</v>
+        <v>4.317532539367676</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -758,7 +758,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D9">
-        <v>0.9982819557189941</v>
+        <v>6.900327682495117</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -772,7 +772,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D10">
-        <v>3.071534633636475</v>
+        <v>1.338942289352417</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -786,7 +786,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D11">
-        <v>6.077768325805664</v>
+        <v>7.340806007385254</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -800,7 +800,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D12">
-        <v>1.922116875648499</v>
+        <v>1.472642421722412</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -814,7 +814,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D13">
-        <v>2.225476264953613</v>
+        <v>1.999656438827515</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -828,7 +828,7 @@
         <v>0.5</v>
       </c>
       <c r="D14">
-        <v>2.125826835632324</v>
+        <v>1.069316983222961</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -842,7 +842,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D15">
-        <v>1.221228003501892</v>
+        <v>1.159691214561462</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -856,7 +856,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D16">
-        <v>1.501566171646118</v>
+        <v>0.9829359650611877</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -870,7 +870,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D17">
-        <v>4.69754695892334</v>
+        <v>1.570908308029175</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -884,7 +884,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D18">
-        <v>3.818681716918945</v>
+        <v>2.586637258529663</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -898,7 +898,7 @@
         <v>25.79999923706055</v>
       </c>
       <c r="D19">
-        <v>16.43043899536133</v>
+        <v>16.3834228515625</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -912,7 +912,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D20">
-        <v>1.245184063911438</v>
+        <v>2.450326204299927</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -926,7 +926,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D21">
-        <v>11.57067012786865</v>
+        <v>20.6215877532959</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -940,7 +940,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D22">
-        <v>18.09657669067383</v>
+        <v>21.35884857177734</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -954,7 +954,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D23">
-        <v>2.287254333496094</v>
+        <v>1.510552406311035</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -968,7 +968,7 @@
         <v>13.89999961853027</v>
       </c>
       <c r="D24">
-        <v>9.277679443359375</v>
+        <v>11.27287673950195</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -982,7 +982,7 @@
         <v>22.60000038146973</v>
       </c>
       <c r="D25">
-        <v>2.085686206817627</v>
+        <v>1.848731756210327</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -996,7 +996,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D26">
-        <v>1.429394364356995</v>
+        <v>0.5886984467506409</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1010,7 +1010,7 @@
         <v>4.5</v>
       </c>
       <c r="D27">
-        <v>2.502203941345215</v>
+        <v>0.9650443196296692</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1024,7 +1024,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D28">
-        <v>3.274449586868286</v>
+        <v>0.9880455136299133</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1038,7 +1038,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D29">
-        <v>2.382556915283203</v>
+        <v>1.082308292388916</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1052,7 +1052,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D30">
-        <v>2.832966327667236</v>
+        <v>1.833928346633911</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1066,7 +1066,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D31">
-        <v>14.20155143737793</v>
+        <v>16.4437313079834</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1080,7 +1080,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D32">
-        <v>2.522000789642334</v>
+        <v>1.710352420806885</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1094,7 +1094,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D33">
-        <v>0.9562209844589233</v>
+        <v>4.975651741027832</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1108,7 +1108,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D34">
-        <v>3.120128154754639</v>
+        <v>2.390920877456665</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1122,7 +1122,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D35">
-        <v>6.868143081665039</v>
+        <v>7.157227516174316</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1136,7 +1136,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D36">
-        <v>8.204709053039551</v>
+        <v>17.40090942382812</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1150,7 +1150,7 @@
         <v>21</v>
       </c>
       <c r="D37">
-        <v>16.20409965515137</v>
+        <v>16.16497993469238</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1164,7 +1164,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D38">
-        <v>2.706070899963379</v>
+        <v>0.9538800120353699</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1178,7 +1178,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D39">
-        <v>2.944496154785156</v>
+        <v>1.27904748916626</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1192,7 +1192,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D40">
-        <v>3.364866971969604</v>
+        <v>0.7006703615188599</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1206,7 +1206,7 @@
         <v>15.69999980926514</v>
       </c>
       <c r="D41">
-        <v>8.38701343536377</v>
+        <v>13.74652862548828</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1220,7 +1220,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D42">
-        <v>1.225238800048828</v>
+        <v>2.064631223678589</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1234,7 +1234,7 @@
         <v>9.5</v>
       </c>
       <c r="D43">
-        <v>3.760703086853027</v>
+        <v>4.643372535705566</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1248,7 +1248,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D44">
-        <v>5.079256057739258</v>
+        <v>5.152399063110352</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1262,7 +1262,7 @@
         <v>15.10000038146973</v>
       </c>
       <c r="D45">
-        <v>9.032694816589355</v>
+        <v>9.485173225402832</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1276,7 +1276,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D46">
-        <v>1.314781665802002</v>
+        <v>5.446926116943359</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1290,7 +1290,7 @@
         <v>10.5</v>
       </c>
       <c r="D47">
-        <v>1.478876352310181</v>
+        <v>4.081327438354492</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1304,7 +1304,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D48">
-        <v>1.797088265419006</v>
+        <v>1.666934251785278</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1318,7 +1318,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D49">
-        <v>1.424503087997437</v>
+        <v>6.880098342895508</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1332,7 +1332,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D50">
-        <v>1.863486170768738</v>
+        <v>1.012498140335083</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1346,7 +1346,7 @@
         <v>3</v>
       </c>
       <c r="D51">
-        <v>3.145459413528442</v>
+        <v>2.176300525665283</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1360,7 +1360,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D52">
-        <v>1.833441019058228</v>
+        <v>1.433535575866699</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1374,7 +1374,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D53">
-        <v>13.0194263458252</v>
+        <v>19.73419952392578</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1388,7 +1388,7 @@
         <v>28.20000076293945</v>
       </c>
       <c r="D54">
-        <v>16.43361854553223</v>
+        <v>19.23755264282227</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1402,7 +1402,7 @@
         <v>15.19999980926514</v>
       </c>
       <c r="D55">
-        <v>6.956589698791504</v>
+        <v>6.984025955200195</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1416,7 +1416,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D56">
-        <v>1.316517472267151</v>
+        <v>2.157576084136963</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1430,7 +1430,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D57">
-        <v>3.102410316467285</v>
+        <v>6.420064926147461</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1444,7 +1444,7 @@
         <v>8.5</v>
       </c>
       <c r="D58">
-        <v>9.556775093078613</v>
+        <v>12.86634826660156</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1458,7 +1458,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D59">
-        <v>8.259713172912598</v>
+        <v>12.31050682067871</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1472,7 +1472,7 @@
         <v>7.5</v>
       </c>
       <c r="D60">
-        <v>0.9862202405929565</v>
+        <v>6.952889442443848</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1486,7 +1486,7 @@
         <v>12.60000038146973</v>
       </c>
       <c r="D61">
-        <v>1.310078501701355</v>
+        <v>5.240677833557129</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1500,7 +1500,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D62">
-        <v>1.014752745628357</v>
+        <v>6.427011013031006</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1514,7 +1514,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D63">
-        <v>3.421671628952026</v>
+        <v>1.239461660385132</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1528,7 +1528,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D64">
-        <v>2.045455932617188</v>
+        <v>1.118093013763428</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1542,7 +1542,7 @@
         <v>26.70000076293945</v>
       </c>
       <c r="D65">
-        <v>14.70870208740234</v>
+        <v>18.9384937286377</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1556,7 +1556,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D66">
-        <v>1.459258675575256</v>
+        <v>1.3051598072052</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1570,7 +1570,7 @@
         <v>20.89999961853027</v>
       </c>
       <c r="D67">
-        <v>10.12253379821777</v>
+        <v>15.59947490692139</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1584,7 +1584,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D68">
-        <v>2.255682229995728</v>
+        <v>1.598088264465332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1598,7 +1598,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D69">
-        <v>2.325880289077759</v>
+        <v>0.8135791420936584</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1612,7 +1612,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D70">
-        <v>3.02461314201355</v>
+        <v>1.722437620162964</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1626,7 +1626,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D71">
-        <v>6.385684490203857</v>
+        <v>6.891709327697754</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1640,7 +1640,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D72">
-        <v>1.422439813613892</v>
+        <v>1.668060541152954</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1654,7 +1654,7 @@
         <v>3.5</v>
       </c>
       <c r="D73">
-        <v>3.163160085678101</v>
+        <v>0.7834485769271851</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1668,7 +1668,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D74">
-        <v>1.474158406257629</v>
+        <v>6.902102947235107</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1682,7 +1682,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D75">
-        <v>2.002578735351562</v>
+        <v>1.261551141738892</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1696,7 +1696,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D76">
-        <v>1.577116966247559</v>
+        <v>1.679419040679932</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1710,7 +1710,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D77">
-        <v>2.845081806182861</v>
+        <v>2.323686838150024</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1724,7 +1724,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D78">
-        <v>1.926403403282166</v>
+        <v>1.582574844360352</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1738,7 +1738,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D79">
-        <v>12.8889045715332</v>
+        <v>12.28491973876953</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -1752,7 +1752,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D80">
-        <v>2.832244157791138</v>
+        <v>0.9577664732933044</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1766,7 +1766,7 @@
         <v>2</v>
       </c>
       <c r="D81">
-        <v>2.997512817382812</v>
+        <v>1.703502655029297</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1780,7 +1780,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D82">
-        <v>1.377847790718079</v>
+        <v>1.961180210113525</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1794,7 +1794,7 @@
         <v>1</v>
       </c>
       <c r="D83">
-        <v>1.169081211090088</v>
+        <v>1.25797438621521</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -1808,7 +1808,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D84">
-        <v>5.864253044128418</v>
+        <v>6.110895156860352</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1822,7 +1822,7 @@
         <v>12.89999961853027</v>
       </c>
       <c r="D85">
-        <v>10.46177101135254</v>
+        <v>14.91711616516113</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1836,7 +1836,7 @@
         <v>2.5</v>
       </c>
       <c r="D86">
-        <v>1.099682688713074</v>
+        <v>0.9273514151573181</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1850,7 +1850,7 @@
         <v>0.5</v>
       </c>
       <c r="D87">
-        <v>1.851447582244873</v>
+        <v>1.147309303283691</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -1864,7 +1864,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D88">
-        <v>3.09396767616272</v>
+        <v>0.8313141465187073</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1878,7 +1878,7 @@
         <v>1</v>
       </c>
       <c r="D89">
-        <v>1.362977504730225</v>
+        <v>1.140362024307251</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1892,7 +1892,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D90">
-        <v>3.887848615646362</v>
+        <v>7.679389953613281</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1906,7 +1906,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D91">
-        <v>1.427196502685547</v>
+        <v>0.8127992749214172</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1920,7 +1920,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D92">
-        <v>1.016257524490356</v>
+        <v>1.436818838119507</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -1934,7 +1934,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D93">
-        <v>2.877681255340576</v>
+        <v>0.9049239754676819</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -1948,7 +1948,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D94">
-        <v>6.202812671661377</v>
+        <v>7.71599006652832</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1962,7 +1962,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D95">
-        <v>3.046549320220947</v>
+        <v>2.182422161102295</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1976,7 +1976,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D96">
-        <v>1.341332793235779</v>
+        <v>5.76750659942627</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1990,7 +1990,7 @@
         <v>12.69999980926514</v>
       </c>
       <c r="D97">
-        <v>5.575499534606934</v>
+        <v>7.85109281539917</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2004,7 +2004,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D98">
-        <v>6.957843780517578</v>
+        <v>10.82625579833984</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2018,7 +2018,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D99">
-        <v>1.575168251991272</v>
+        <v>2.839792966842651</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2032,7 +2032,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D100">
-        <v>1.18920111656189</v>
+        <v>1.615350961685181</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2046,7 +2046,7 @@
         <v>15.60000038146973</v>
       </c>
       <c r="D101">
-        <v>14.60837364196777</v>
+        <v>17.46413993835449</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2060,7 +2060,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D102">
-        <v>2.849066495895386</v>
+        <v>2.214880704879761</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2074,7 +2074,7 @@
         <v>12.5</v>
       </c>
       <c r="D103">
-        <v>8.31315803527832</v>
+        <v>12.29971504211426</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2088,7 +2088,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D104">
-        <v>3.870033502578735</v>
+        <v>6.106075763702393</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2102,7 +2102,7 @@
         <v>17.60000038146973</v>
       </c>
       <c r="D105">
-        <v>6.374359607696533</v>
+        <v>12.86953544616699</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2116,7 +2116,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D106">
-        <v>1.536553502082825</v>
+        <v>8.955776214599609</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2130,7 +2130,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D107">
-        <v>2.563461303710938</v>
+        <v>1.098964214324951</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2144,7 +2144,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D108">
-        <v>2.823914051055908</v>
+        <v>2.085357427597046</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2158,7 +2158,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D109">
-        <v>8.109259605407715</v>
+        <v>1.359601259231567</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2172,7 +2172,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D110">
-        <v>1.651050090789795</v>
+        <v>0.7113744020462036</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2186,7 +2186,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D111">
-        <v>6.571500778198242</v>
+        <v>8.129631996154785</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2200,7 +2200,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D112">
-        <v>2.742622137069702</v>
+        <v>1.332274436950684</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2214,7 +2214,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D113">
-        <v>2.35822319984436</v>
+        <v>1.449896335601807</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2228,7 +2228,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D114">
-        <v>7.182223320007324</v>
+        <v>8.828054428100586</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2242,7 +2242,7 @@
         <v>13.10000038146973</v>
       </c>
       <c r="D115">
-        <v>6.758503913879395</v>
+        <v>7.380096435546875</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2256,7 +2256,7 @@
         <v>39.70000076293945</v>
       </c>
       <c r="D116">
-        <v>1.460447072982788</v>
+        <v>2.980502367019653</v>
       </c>
     </row>
   </sheetData>
